--- a/outputs/marine_equipment/Отгрузка_образец.xlsx
+++ b/outputs/marine_equipment/Отгрузка_образец.xlsx
@@ -926,7 +926,11 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="I18" s="12" t="n"/>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>Б/у</t>
+        </is>
+      </c>
       <c r="J18" s="12" t="n">
         <v>2</v>
       </c>
